--- a/ssp_modeling/scenario_mapping/ssp_bulgaria_transformation_dec_8.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_bulgaria_transformation_dec_8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/sisepuede_modeling/ssp_bulgaria/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711AA792-4E9F-3142-BC39-F9B0DF8DF7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188182A5-E292-714B-AFB3-296CBB19667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23320" yWindow="3140" windowWidth="38400" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="500" yWindow="1040" windowWidth="37500" windowHeight="26840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -1635,7 +1635,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1730,9 +1730,6 @@
     <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -1771,13 +1768,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1790,6 +1781,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2106,24 +2100,24 @@
     <col min="4" max="4" width="31.6640625" style="4" customWidth="1"/>
     <col min="5" max="5" width="62.5" style="4" customWidth="1"/>
     <col min="6" max="6" width="33.1640625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="75.83203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="39.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="75.83203125" style="4" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="39.33203125" style="4" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="13.83203125" style="4" customWidth="1"/>
     <col min="10" max="10" width="14.1640625" style="4" customWidth="1"/>
-    <col min="11" max="12" width="35" style="4" customWidth="1"/>
-    <col min="13" max="13" width="31.5" style="36" customWidth="1"/>
-    <col min="14" max="14" width="19.83203125" style="35" customWidth="1"/>
-    <col min="15" max="16" width="20.5" style="37" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5" style="37" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5" style="39" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="35" style="4" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="31.5" style="35" customWidth="1"/>
+    <col min="14" max="14" width="19.83203125" style="34" customWidth="1"/>
+    <col min="15" max="16" width="20.5" style="36" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5" style="37" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5" style="36" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5" style="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="4" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="39" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
@@ -2141,13 +2135,13 @@
       <c r="G1" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="H1" s="48" t="s">
+      <c r="H1" s="46" t="s">
         <v>433</v>
       </c>
-      <c r="I1" s="48" t="s">
+      <c r="I1" s="46" t="s">
         <v>431</v>
       </c>
-      <c r="J1" s="48" t="s">
+      <c r="J1" s="46" t="s">
         <v>432</v>
       </c>
       <c r="K1" s="7" t="s">
@@ -2217,7 +2211,7 @@
       <c r="A3" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="17" t="s">
@@ -2314,16 +2308,16 @@
       <c r="F5" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="G5" s="46" t="s">
+      <c r="G5" s="45" t="s">
         <v>414</v>
       </c>
-      <c r="H5" s="46" t="s">
+      <c r="H5" s="45" t="s">
         <v>445</v>
       </c>
-      <c r="I5" s="46">
-        <v>1</v>
-      </c>
-      <c r="J5" s="46">
+      <c r="I5" s="45">
+        <v>1</v>
+      </c>
+      <c r="J5" s="45">
         <v>1</v>
       </c>
       <c r="K5" s="12"/>
@@ -2400,14 +2394,14 @@
       <c r="F7" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="G7" s="43" t="s">
+      <c r="G7" s="42" t="s">
         <v>413</v>
       </c>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43">
+      <c r="H7" s="42"/>
+      <c r="I7" s="42">
         <v>0</v>
       </c>
-      <c r="J7" s="43">
+      <c r="J7" s="42">
         <v>1</v>
       </c>
       <c r="K7" s="12"/>
@@ -2419,7 +2413,7 @@
         <v>12</v>
       </c>
       <c r="O7" s="16"/>
-      <c r="P7" s="42">
+      <c r="P7" s="41">
         <v>1</v>
       </c>
       <c r="Q7" s="10"/>
@@ -2472,7 +2466,7 @@
       <c r="O8" s="16">
         <v>0.25</v>
       </c>
-      <c r="P8" s="42">
+      <c r="P8" s="41">
         <v>1</v>
       </c>
       <c r="Q8" s="10"/>
@@ -2515,7 +2509,7 @@
         <v>12</v>
       </c>
       <c r="O9" s="16"/>
-      <c r="P9" s="42">
+      <c r="P9" s="41">
         <v>1</v>
       </c>
       <c r="Q9" s="10"/>
@@ -2566,7 +2560,7 @@
       <c r="O10" s="16">
         <v>0.5</v>
       </c>
-      <c r="P10" s="42">
+      <c r="P10" s="41">
         <v>1</v>
       </c>
       <c r="Q10" s="10"/>
@@ -2605,7 +2599,7 @@
         <v>12</v>
       </c>
       <c r="O11" s="16"/>
-      <c r="P11" s="42">
+      <c r="P11" s="41">
         <v>1</v>
       </c>
       <c r="Q11" s="10"/>
@@ -2644,7 +2638,7 @@
         <v>12</v>
       </c>
       <c r="O12" s="16"/>
-      <c r="P12" s="42">
+      <c r="P12" s="41">
         <v>1</v>
       </c>
       <c r="Q12" s="10"/>
@@ -2695,7 +2689,7 @@
       <c r="O13" s="16">
         <v>0.5</v>
       </c>
-      <c r="P13" s="42">
+      <c r="P13" s="41">
         <v>1</v>
       </c>
       <c r="Q13" s="10"/>
@@ -2746,7 +2740,7 @@
       <c r="O14" s="16">
         <v>0.25</v>
       </c>
-      <c r="P14" s="42">
+      <c r="P14" s="41">
         <v>1</v>
       </c>
       <c r="Q14" s="10"/>
@@ -2791,7 +2785,7 @@
         <v>12</v>
       </c>
       <c r="O15" s="16"/>
-      <c r="P15" s="42">
+      <c r="P15" s="41">
         <v>1</v>
       </c>
       <c r="Q15" s="10"/>
@@ -2853,36 +2847,36 @@
       <c r="B17" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="C17" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="51" t="s">
+      <c r="E17" s="48" t="s">
         <v>257</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="44" t="s">
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="L17" s="44" t="s">
+      <c r="L17" s="43" t="s">
         <v>260</v>
       </c>
-      <c r="M17" s="52">
+      <c r="M17" s="49">
         <v>0.3</v>
       </c>
-      <c r="N17" s="53">
+      <c r="N17" s="50">
         <v>7</v>
       </c>
-      <c r="O17" s="45"/>
-      <c r="P17" s="45"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
@@ -2928,11 +2922,9 @@
       <c r="N18" s="13">
         <v>7</v>
       </c>
-      <c r="O18" s="16">
-        <v>1</v>
-      </c>
+      <c r="O18" s="16"/>
       <c r="P18" s="16">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="Q18" s="10"/>
       <c r="R18" s="11"/>
@@ -2945,35 +2937,33 @@
       <c r="B19" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="43" t="s">
         <v>265</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="43" t="s">
         <v>266</v>
       </c>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="15">
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="49">
         <v>0.1</v>
       </c>
-      <c r="N19" s="13">
+      <c r="N19" s="50">
         <v>7</v>
       </c>
-      <c r="O19" s="16">
-        <v>1</v>
-      </c>
+      <c r="O19" s="16"/>
       <c r="P19" s="16">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="Q19" s="10"/>
       <c r="R19" s="11"/>
@@ -3016,11 +3006,9 @@
       <c r="N20" s="13">
         <v>7</v>
       </c>
-      <c r="O20" s="16">
-        <v>1</v>
-      </c>
+      <c r="O20" s="16"/>
       <c r="P20" s="16">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="Q20" s="10"/>
       <c r="R20" s="11"/>
@@ -3063,11 +3051,9 @@
       <c r="N21" s="13">
         <v>7</v>
       </c>
-      <c r="O21" s="16">
-        <v>1</v>
-      </c>
+      <c r="O21" s="16"/>
       <c r="P21" s="16">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="Q21" s="10"/>
       <c r="R21" s="11"/>
@@ -3168,47 +3154,47 @@
       <c r="B24" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D24" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="48" t="s">
         <v>279</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="43" t="s">
         <v>426</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="43" t="s">
         <v>437</v>
       </c>
-      <c r="I24" s="12">
-        <v>1</v>
-      </c>
-      <c r="J24" s="12">
-        <v>1</v>
-      </c>
-      <c r="K24" s="26" t="s">
+      <c r="I24" s="43">
+        <v>1</v>
+      </c>
+      <c r="J24" s="43">
+        <v>1</v>
+      </c>
+      <c r="K24" s="43" t="s">
         <v>281</v>
       </c>
-      <c r="L24" s="26" t="s">
+      <c r="L24" s="43" t="s">
         <v>282</v>
       </c>
-      <c r="M24" s="15">
+      <c r="M24" s="49">
         <v>0.2</v>
       </c>
-      <c r="N24" s="13">
+      <c r="N24" s="50">
         <v>12</v>
       </c>
       <c r="O24" s="16">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="P24" s="16">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="Q24" s="10"/>
       <c r="R24" s="11"/>
@@ -3293,10 +3279,10 @@
         <v>12</v>
       </c>
       <c r="O26" s="16">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="P26" s="16">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="Q26" s="28"/>
       <c r="R26" s="29"/>
@@ -3368,14 +3354,14 @@
       <c r="F28" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="G28" s="43" t="s">
+      <c r="G28" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43">
-        <v>1</v>
-      </c>
-      <c r="J28" s="43">
+      <c r="H28" s="42"/>
+      <c r="I28" s="42">
+        <v>1</v>
+      </c>
+      <c r="J28" s="42">
         <v>1</v>
       </c>
       <c r="K28" s="12"/>
@@ -3415,14 +3401,14 @@
       <c r="F29" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="G29" s="43" t="s">
+      <c r="G29" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43">
-        <v>1</v>
-      </c>
-      <c r="J29" s="43">
+      <c r="H29" s="42"/>
+      <c r="I29" s="42">
+        <v>1</v>
+      </c>
+      <c r="J29" s="42">
         <v>1</v>
       </c>
       <c r="K29" s="12"/>
@@ -3450,40 +3436,42 @@
       <c r="B30" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="E30" s="43" t="s">
         <v>296</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="43" t="s">
         <v>297</v>
       </c>
-      <c r="G30" s="26" t="s">
+      <c r="G30" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="H30" s="26" t="s">
+      <c r="H30" s="43" t="s">
         <v>438</v>
       </c>
-      <c r="I30" s="26">
+      <c r="I30" s="43">
         <v>0</v>
       </c>
-      <c r="J30" s="26">
-        <v>1</v>
-      </c>
-      <c r="K30" s="44"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="15" t="s">
+      <c r="J30" s="43">
+        <v>1</v>
+      </c>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="49" t="s">
         <v>298</v>
       </c>
-      <c r="N30" s="47">
+      <c r="N30" s="50">
         <v>12</v>
       </c>
-      <c r="O30" s="49"/>
-      <c r="P30" s="45">
+      <c r="O30" s="44">
+        <v>1</v>
+      </c>
+      <c r="P30" s="44">
         <v>1</v>
       </c>
       <c r="Q30" s="10"/>
@@ -3686,7 +3674,7 @@
         <v>12</v>
       </c>
       <c r="O35" s="16"/>
-      <c r="P35" s="42">
+      <c r="P35" s="41">
         <v>1</v>
       </c>
       <c r="Q35" s="10"/>
@@ -3735,7 +3723,7 @@
       <c r="O36" s="16">
         <v>0.5</v>
       </c>
-      <c r="P36" s="42">
+      <c r="P36" s="41">
         <v>1</v>
       </c>
       <c r="Q36" s="10"/>
@@ -3784,7 +3772,7 @@
       <c r="O37" s="16">
         <v>0.5</v>
       </c>
-      <c r="P37" s="42">
+      <c r="P37" s="41">
         <v>1</v>
       </c>
       <c r="Q37" s="10"/>
@@ -3917,7 +3905,7 @@
       <c r="O40" s="16">
         <v>0.5</v>
       </c>
-      <c r="P40" s="42">
+      <c r="P40" s="41">
         <v>1</v>
       </c>
       <c r="Q40" s="10"/>
@@ -3960,7 +3948,7 @@
         <v>12</v>
       </c>
       <c r="O41" s="16"/>
-      <c r="P41" s="42">
+      <c r="P41" s="41">
         <v>1</v>
       </c>
       <c r="Q41" s="10"/>
@@ -4003,7 +3991,7 @@
         <v>12</v>
       </c>
       <c r="O42" s="16"/>
-      <c r="P42" s="42">
+      <c r="P42" s="41">
         <v>1</v>
       </c>
       <c r="Q42" s="10"/>
@@ -4042,7 +4030,7 @@
         <v>12</v>
       </c>
       <c r="O43" s="16"/>
-      <c r="P43" s="42">
+      <c r="P43" s="41">
         <v>1</v>
       </c>
       <c r="Q43" s="10"/>
@@ -4089,7 +4077,7 @@
       <c r="O44" s="16">
         <v>0.5</v>
       </c>
-      <c r="P44" s="42">
+      <c r="P44" s="41">
         <v>1</v>
       </c>
       <c r="Q44" s="10"/>
@@ -4140,7 +4128,7 @@
       <c r="O45" s="16">
         <v>0.5</v>
       </c>
-      <c r="P45" s="42">
+      <c r="P45" s="41">
         <v>1</v>
       </c>
       <c r="Q45" s="10"/>
@@ -4191,7 +4179,7 @@
       <c r="O46" s="16">
         <v>0.5</v>
       </c>
-      <c r="P46" s="42">
+      <c r="P46" s="41">
         <v>1</v>
       </c>
       <c r="Q46" s="10"/>
@@ -4238,7 +4226,7 @@
       <c r="O47" s="16">
         <v>0.5</v>
       </c>
-      <c r="P47" s="42">
+      <c r="P47" s="41">
         <v>1</v>
       </c>
       <c r="Q47" s="10"/>
@@ -4287,7 +4275,7 @@
         <v>12</v>
       </c>
       <c r="O48" s="16"/>
-      <c r="P48" s="42">
+      <c r="P48" s="41">
         <v>1</v>
       </c>
       <c r="Q48" s="10"/>
@@ -4338,7 +4326,7 @@
       <c r="O49" s="16">
         <v>0.5</v>
       </c>
-      <c r="P49" s="42">
+      <c r="P49" s="41">
         <v>1</v>
       </c>
       <c r="Q49" s="10"/>
@@ -4387,7 +4375,7 @@
         <v>12</v>
       </c>
       <c r="O50" s="16"/>
-      <c r="P50" s="42">
+      <c r="P50" s="41">
         <v>1</v>
       </c>
       <c r="Q50" s="10"/>
@@ -4401,28 +4389,28 @@
       <c r="B51" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="C51" s="26" t="s">
+      <c r="C51" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="D51" s="26" t="s">
+      <c r="D51" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="E51" s="26" t="s">
+      <c r="E51" s="43" t="s">
         <v>359</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="43" t="s">
         <v>360</v>
       </c>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="12"/>
-      <c r="M51" s="18">
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+      <c r="L51" s="43"/>
+      <c r="M51" s="49">
         <v>0.85</v>
       </c>
-      <c r="N51" s="13">
+      <c r="N51" s="50">
         <v>12</v>
       </c>
       <c r="O51" s="16"/>
@@ -4440,32 +4428,32 @@
       <c r="B52" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="C52" s="26" t="s">
+      <c r="C52" s="43" t="s">
         <v>169</v>
       </c>
-      <c r="D52" s="26" t="s">
+      <c r="D52" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="E52" s="26" t="s">
+      <c r="E52" s="43" t="s">
         <v>361</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="F52" s="43" t="s">
         <v>362</v>
       </c>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12" t="s">
+      <c r="G52" s="43"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="43" t="s">
         <v>363</v>
       </c>
-      <c r="L52" s="12" t="s">
+      <c r="L52" s="43" t="s">
         <v>364</v>
       </c>
-      <c r="M52" s="18">
+      <c r="M52" s="49">
         <v>0.9</v>
       </c>
-      <c r="N52" s="13">
+      <c r="N52" s="50">
         <v>12</v>
       </c>
       <c r="O52" s="16"/>
@@ -4483,40 +4471,40 @@
       <c r="B53" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="C53" s="26" t="s">
+      <c r="C53" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="D53" s="26" t="s">
+      <c r="D53" s="43" t="s">
         <v>174</v>
       </c>
-      <c r="E53" s="26" t="s">
+      <c r="E53" s="43" t="s">
         <v>366</v>
       </c>
-      <c r="F53" s="12" t="s">
+      <c r="F53" s="43" t="s">
         <v>367</v>
       </c>
-      <c r="G53" s="12" t="s">
+      <c r="G53" s="43" t="s">
         <v>443</v>
       </c>
-      <c r="H53" s="12" t="s">
+      <c r="H53" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="I53" s="12">
+      <c r="I53" s="43">
         <v>0</v>
       </c>
-      <c r="J53" s="12">
-        <v>1</v>
-      </c>
-      <c r="K53" s="12" t="s">
+      <c r="J53" s="43">
+        <v>1</v>
+      </c>
+      <c r="K53" s="43" t="s">
         <v>368</v>
       </c>
-      <c r="L53" s="12" t="s">
+      <c r="L53" s="43" t="s">
         <v>369</v>
       </c>
-      <c r="M53" s="18" t="s">
+      <c r="M53" s="49" t="s">
         <v>370</v>
       </c>
-      <c r="N53" s="13">
+      <c r="N53" s="50">
         <v>12</v>
       </c>
       <c r="O53" s="16"/>
@@ -4534,32 +4522,32 @@
       <c r="B54" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="C54" s="26" t="s">
+      <c r="C54" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="D54" s="26" t="s">
+      <c r="D54" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="E54" s="26" t="s">
+      <c r="E54" s="43" t="s">
         <v>371</v>
       </c>
-      <c r="F54" s="12" t="s">
+      <c r="F54" s="43" t="s">
         <v>367</v>
       </c>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12" t="s">
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43" t="s">
         <v>372</v>
       </c>
-      <c r="L54" s="12" t="s">
+      <c r="L54" s="43" t="s">
         <v>373</v>
       </c>
-      <c r="M54" s="18" t="s">
+      <c r="M54" s="49" t="s">
         <v>374</v>
       </c>
-      <c r="N54" s="13">
+      <c r="N54" s="50">
         <v>12</v>
       </c>
       <c r="O54" s="16"/>
@@ -4577,32 +4565,32 @@
       <c r="B55" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="C55" s="26" t="s">
+      <c r="C55" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="D55" s="26" t="s">
+      <c r="D55" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="E55" s="26" t="s">
+      <c r="E55" s="43" t="s">
         <v>375</v>
       </c>
-      <c r="F55" s="12" t="s">
+      <c r="F55" s="43" t="s">
         <v>367</v>
       </c>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
-      <c r="K55" s="12" t="s">
+      <c r="G55" s="43"/>
+      <c r="H55" s="43"/>
+      <c r="I55" s="43"/>
+      <c r="J55" s="43"/>
+      <c r="K55" s="43" t="s">
         <v>376</v>
       </c>
-      <c r="L55" s="12" t="s">
+      <c r="L55" s="43" t="s">
         <v>377</v>
       </c>
-      <c r="M55" s="18" t="s">
+      <c r="M55" s="49" t="s">
         <v>378</v>
       </c>
-      <c r="N55" s="13">
+      <c r="N55" s="50">
         <v>12</v>
       </c>
       <c r="O55" s="16"/>
@@ -4620,40 +4608,40 @@
       <c r="B56" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="43" t="s">
         <v>183</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="43" t="s">
         <v>379</v>
       </c>
-      <c r="F56" s="12" t="s">
+      <c r="F56" s="43" t="s">
         <v>380</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="G56" s="43" t="s">
         <v>421</v>
       </c>
-      <c r="H56" s="12" t="s">
+      <c r="H56" s="43" t="s">
         <v>441</v>
       </c>
-      <c r="I56" s="12">
+      <c r="I56" s="43">
         <v>0</v>
       </c>
-      <c r="J56" s="12">
-        <v>1</v>
-      </c>
-      <c r="K56" s="12" t="s">
+      <c r="J56" s="43">
+        <v>1</v>
+      </c>
+      <c r="K56" s="43" t="s">
         <v>381</v>
       </c>
-      <c r="L56" s="12" t="s">
+      <c r="L56" s="43" t="s">
         <v>382</v>
       </c>
-      <c r="M56" s="18">
+      <c r="M56" s="49">
         <v>0.3</v>
       </c>
-      <c r="N56" s="13">
+      <c r="N56" s="50">
         <v>12</v>
       </c>
       <c r="O56" s="16"/>
@@ -4671,36 +4659,36 @@
       <c r="B57" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="E57" s="12" t="s">
+      <c r="E57" s="43" t="s">
         <v>383</v>
       </c>
-      <c r="F57" s="12" t="s">
+      <c r="F57" s="43" t="s">
         <v>384</v>
       </c>
-      <c r="G57" s="12" t="s">
+      <c r="G57" s="43" t="s">
         <v>420</v>
       </c>
-      <c r="H57" s="12" t="s">
+      <c r="H57" s="43" t="s">
         <v>442</v>
       </c>
-      <c r="I57" s="12">
-        <v>1</v>
-      </c>
-      <c r="J57" s="12">
-        <v>1</v>
-      </c>
-      <c r="K57" s="12"/>
-      <c r="L57" s="12"/>
-      <c r="M57" s="15" t="s">
+      <c r="I57" s="43">
+        <v>1</v>
+      </c>
+      <c r="J57" s="43">
+        <v>1</v>
+      </c>
+      <c r="K57" s="43"/>
+      <c r="L57" s="43"/>
+      <c r="M57" s="49" t="s">
         <v>385</v>
       </c>
-      <c r="N57" s="13">
+      <c r="N57" s="50">
         <v>12</v>
       </c>
       <c r="O57" s="16">
@@ -4720,40 +4708,40 @@
       <c r="B58" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="D58" s="22" t="s">
+      <c r="D58" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="E58" s="22" t="s">
+      <c r="E58" s="48" t="s">
         <v>386</v>
       </c>
-      <c r="F58" s="22" t="s">
+      <c r="F58" s="48" t="s">
         <v>387</v>
       </c>
-      <c r="G58" s="12" t="s">
+      <c r="G58" s="43" t="s">
         <v>418</v>
       </c>
-      <c r="H58" s="12" t="s">
+      <c r="H58" s="43" t="s">
         <v>442</v>
       </c>
-      <c r="I58" s="12">
-        <v>1</v>
-      </c>
-      <c r="J58" s="12">
-        <v>1</v>
-      </c>
-      <c r="K58" s="12" t="s">
+      <c r="I58" s="43">
+        <v>1</v>
+      </c>
+      <c r="J58" s="43">
+        <v>1</v>
+      </c>
+      <c r="K58" s="43" t="s">
         <v>388</v>
       </c>
-      <c r="L58" s="12" t="s">
+      <c r="L58" s="43" t="s">
         <v>389</v>
       </c>
-      <c r="M58" s="15">
+      <c r="M58" s="49">
         <v>0.85</v>
       </c>
-      <c r="N58" s="13">
+      <c r="N58" s="50">
         <v>12</v>
       </c>
       <c r="O58" s="16">
@@ -4773,42 +4761,42 @@
       <c r="B59" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="C59" s="26" t="s">
+      <c r="C59" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="D59" s="26" t="s">
+      <c r="D59" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="E59" s="26" t="s">
+      <c r="E59" s="43" t="s">
         <v>390</v>
       </c>
-      <c r="F59" s="26" t="s">
+      <c r="F59" s="43" t="s">
         <v>391</v>
       </c>
-      <c r="G59" s="26" t="s">
+      <c r="G59" s="43" t="s">
         <v>429</v>
       </c>
-      <c r="H59" s="12" t="s">
+      <c r="H59" s="43" t="s">
         <v>442</v>
       </c>
-      <c r="I59" s="26">
-        <v>1</v>
-      </c>
-      <c r="J59" s="26">
-        <v>1</v>
-      </c>
-      <c r="K59" s="44"/>
-      <c r="L59" s="44"/>
-      <c r="M59" s="15">
+      <c r="I59" s="43">
+        <v>1</v>
+      </c>
+      <c r="J59" s="43">
+        <v>1</v>
+      </c>
+      <c r="K59" s="43"/>
+      <c r="L59" s="43"/>
+      <c r="M59" s="49">
         <v>0.85</v>
       </c>
-      <c r="N59" s="47">
+      <c r="N59" s="50">
         <v>12</v>
       </c>
-      <c r="O59" s="45">
+      <c r="O59" s="44">
         <v>0.5</v>
       </c>
-      <c r="P59" s="45">
+      <c r="P59" s="44">
         <v>0.5</v>
       </c>
       <c r="Q59" s="31"/>
@@ -4824,36 +4812,36 @@
       <c r="B60" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="E60" s="12" t="s">
+      <c r="E60" s="43" t="s">
         <v>392</v>
       </c>
-      <c r="F60" s="12" t="s">
+      <c r="F60" s="43" t="s">
         <v>393</v>
       </c>
-      <c r="G60" s="12" t="s">
+      <c r="G60" s="43" t="s">
         <v>419</v>
       </c>
-      <c r="H60" s="12" t="s">
+      <c r="H60" s="43" t="s">
         <v>442</v>
       </c>
-      <c r="I60" s="12">
-        <v>1</v>
-      </c>
-      <c r="J60" s="12">
-        <v>1</v>
-      </c>
-      <c r="K60" s="12"/>
-      <c r="L60" s="12"/>
-      <c r="M60" s="15">
+      <c r="I60" s="43">
+        <v>1</v>
+      </c>
+      <c r="J60" s="43">
+        <v>1</v>
+      </c>
+      <c r="K60" s="43"/>
+      <c r="L60" s="43"/>
+      <c r="M60" s="49">
         <v>0.85</v>
       </c>
-      <c r="N60" s="13">
+      <c r="N60" s="50">
         <v>12</v>
       </c>
       <c r="O60" s="16">
@@ -4875,32 +4863,32 @@
       <c r="B61" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="43" t="s">
         <v>198</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="43" t="s">
         <v>394</v>
       </c>
-      <c r="F61" s="12" t="s">
+      <c r="F61" s="43" t="s">
         <v>395</v>
       </c>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="12"/>
-      <c r="J61" s="12"/>
-      <c r="K61" s="12" t="s">
+      <c r="G61" s="43"/>
+      <c r="H61" s="43"/>
+      <c r="I61" s="43"/>
+      <c r="J61" s="43"/>
+      <c r="K61" s="43" t="s">
         <v>396</v>
       </c>
-      <c r="L61" s="12" t="s">
+      <c r="L61" s="43" t="s">
         <v>397</v>
       </c>
-      <c r="M61" s="32">
-        <v>1</v>
-      </c>
-      <c r="N61" s="13">
+      <c r="M61" s="51">
+        <v>1</v>
+      </c>
+      <c r="N61" s="50">
         <v>12</v>
       </c>
       <c r="O61" s="16">
@@ -4922,40 +4910,40 @@
       <c r="B62" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="43" t="s">
         <v>201</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="E62" s="43" t="s">
         <v>398</v>
       </c>
-      <c r="F62" s="12" t="s">
+      <c r="F62" s="43" t="s">
         <v>399</v>
       </c>
-      <c r="G62" s="12" t="s">
+      <c r="G62" s="43" t="s">
         <v>422</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="H62" s="43" t="s">
         <v>441</v>
       </c>
-      <c r="I62" s="12">
+      <c r="I62" s="43">
         <v>0</v>
       </c>
-      <c r="J62" s="12">
-        <v>1</v>
-      </c>
-      <c r="K62" s="12" t="s">
+      <c r="J62" s="43">
+        <v>1</v>
+      </c>
+      <c r="K62" s="43" t="s">
         <v>400</v>
       </c>
-      <c r="L62" s="12" t="s">
+      <c r="L62" s="43" t="s">
         <v>401</v>
       </c>
-      <c r="M62" s="18">
+      <c r="M62" s="49">
         <v>0.95</v>
       </c>
-      <c r="N62" s="13">
+      <c r="N62" s="50">
         <v>12</v>
       </c>
       <c r="O62" s="16">
@@ -4964,9 +4952,9 @@
       <c r="P62" s="16">
         <v>0.5</v>
       </c>
-      <c r="Q62" s="38"/>
-      <c r="R62" s="37"/>
-      <c r="S62" s="39"/>
+      <c r="Q62" s="37"/>
+      <c r="R62" s="36"/>
+      <c r="S62" s="38"/>
       <c r="T62"/>
       <c r="U62"/>
     </row>
@@ -4983,8 +4971,8 @@
       <c r="J63" s="19"/>
       <c r="K63" s="19"/>
       <c r="L63" s="19"/>
-      <c r="M63" s="34"/>
-      <c r="N63" s="33"/>
+      <c r="M63" s="33"/>
+      <c r="N63" s="32"/>
       <c r="O63" s="29"/>
       <c r="P63" s="29"/>
     </row>
@@ -5001,8 +4989,8 @@
       <c r="J64" s="19"/>
       <c r="K64" s="19"/>
       <c r="L64" s="19"/>
-      <c r="M64" s="34"/>
-      <c r="N64" s="33"/>
+      <c r="M64" s="33"/>
+      <c r="N64" s="32"/>
       <c r="O64" s="29"/>
       <c r="P64" s="29"/>
     </row>
@@ -5019,8 +5007,8 @@
       <c r="J65" s="19"/>
       <c r="K65" s="19"/>
       <c r="L65" s="19"/>
-      <c r="M65" s="34"/>
-      <c r="N65" s="33"/>
+      <c r="M65" s="33"/>
+      <c r="N65" s="32"/>
       <c r="O65" s="29"/>
       <c r="P65" s="29"/>
     </row>
